--- a/results_logic/Results_By_Date.xlsx
+++ b/results_logic/Results_By_Date.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14-Apr-2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15-Apr-2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-Apr-2026" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17-Apr-2026" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40166,4 +40167,3822 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BA28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="14" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="16" customWidth="1" min="47" max="47"/>
+    <col width="14" customWidth="1" min="48" max="48"/>
+    <col width="14" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Results  ·  17 Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>▶  Sorted by Sales YoY Q%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Result Date</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Industry Group</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Subsector</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Indices</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Market Cap (Cr)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Screener Ticker</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Net Profit (Cr)</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>PAT Margin%</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Sales QoQ%</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA QoQ%</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>NP QoQ%</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>EPS QoQ%</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>PAT Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Sales YoY Q%</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA YoY Q%</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>NP YoY Q%</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>EPS YoY Q%</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>Prev Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Prev Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>Prev Qtr NP</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Prev Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>LY Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>LY Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>LY Qtr NP</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>LY Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>FY Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>FY EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>FY NP (Cr)</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>FY EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>FY PAT Margin%</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>FY Sales YoY%</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>FY EBITDA YoY%</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>FY NP YoY%</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>FY EPS YoY%</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>FY PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Prev FY Sales</t>
+        </is>
+      </c>
+      <c r="AY3" s="3" t="inlineStr">
+        <is>
+          <t>Prev FY EBITDA</t>
+        </is>
+      </c>
+      <c r="AZ3" s="3" t="inlineStr">
+        <is>
+          <t>Prev FY NP</t>
+        </is>
+      </c>
+      <c r="BA3" s="3" t="inlineStr">
+        <is>
+          <t>Prev FY EPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Lloyds Luxuries</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="n">
+        <v>197</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>LLOYDS</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S4" s="10" t="inlineStr"/>
+      <c r="T4" s="10" t="inlineStr"/>
+      <c r="U4" s="10" t="inlineStr"/>
+      <c r="V4" s="12" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="W4" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="X4" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y4" s="10" t="inlineStr"/>
+      <c r="Z4" s="10" t="inlineStr"/>
+      <c r="AA4" s="10" t="inlineStr"/>
+      <c r="AB4" s="12" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="AC4" s="12" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AD4" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE4" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF4" s="10" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AG4" s="10" t="n">
+        <v>-14.55</v>
+      </c>
+      <c r="AH4" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI4" s="10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ4" s="10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AK4" s="10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL4" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="AM4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="10" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AO4" s="10" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="AP4" s="10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ4" s="10" t="n">
+        <v>-55.74</v>
+      </c>
+      <c r="AR4" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AS4" s="10" t="inlineStr"/>
+      <c r="AT4" s="10" t="inlineStr"/>
+      <c r="AU4" s="10" t="inlineStr"/>
+      <c r="AV4" s="12" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AW4" s="11" t="n">
+        <v>-40.52</v>
+      </c>
+      <c r="AX4" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AY4" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ4" s="10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BA4" s="10" t="n">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>M B Agro Prod.</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="13" t="n">
+        <v>4430</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>506</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>395</v>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="P5" s="13" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q5" s="13" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="R5" s="15" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="S5" s="15" t="n">
+        <v>-37.9</v>
+      </c>
+      <c r="T5" s="14" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U5" s="14" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="V5" s="15" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="W5" s="14" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="X5" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y5" s="14" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="Z5" s="14" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA5" s="14" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="AB5" s="15" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="AC5" s="14" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AD5" s="13" t="n">
+        <v>612</v>
+      </c>
+      <c r="AE5" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF5" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG5" s="13" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH5" s="13" t="n">
+        <v>297</v>
+      </c>
+      <c r="AI5" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ5" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK5" s="13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL5" s="13" t="n">
+        <v>1867</v>
+      </c>
+      <c r="AM5" s="13" t="n">
+        <v>227</v>
+      </c>
+      <c r="AN5" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO5" s="13" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="AP5" s="13" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AQ5" s="13" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AR5" s="14" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AS5" s="14" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AT5" s="14" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="AU5" s="14" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="AV5" s="15" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AW5" s="14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AX5" s="13" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AY5" s="13" t="n">
+        <v>145</v>
+      </c>
+      <c r="AZ5" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="BA5" s="13" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="n">
+        <v>6175</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>472</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>327</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="R6" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="S6" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T6" s="12" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U6" s="12" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V6" s="12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W6" s="12" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="X6" s="12" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AA6" s="12" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AB6" s="12" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AC6" s="12" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AD6" s="10" t="n">
+        <v>306</v>
+      </c>
+      <c r="AE6" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="AF6" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG6" s="10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH6" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="AI6" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ6" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AK6" s="10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL6" s="10" t="n">
+        <v>1165</v>
+      </c>
+      <c r="AM6" s="10" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN6" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO6" s="10" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AP6" s="10" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AQ6" s="10" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AR6" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AS6" s="12" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AT6" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU6" s="12" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AV6" s="12" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AW6" s="12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AX6" s="10" t="n">
+        <v>965</v>
+      </c>
+      <c r="AY6" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="AZ6" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="BA6" s="10" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Other Financial Services</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150, Nifty 500</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>31827</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>4340</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>1058</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>319</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>233</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="P7" s="13" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="S7" s="15" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="T7" s="15" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="U7" s="15" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="V7" s="15" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="W7" s="15" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X7" s="14" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Y7" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Z7" s="14" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AA7" s="14" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AB7" s="14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC7" s="14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD7" s="13" t="n">
+        <v>1082</v>
+      </c>
+      <c r="AE7" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF7" s="13" t="n">
+        <v>242</v>
+      </c>
+      <c r="AG7" s="13" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AH7" s="13" t="n">
+        <v>813</v>
+      </c>
+      <c r="AI7" s="13" t="n">
+        <v>232</v>
+      </c>
+      <c r="AJ7" s="13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK7" s="13" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AL7" s="13" t="n">
+        <v>3649</v>
+      </c>
+      <c r="AM7" s="13" t="n">
+        <v>1085</v>
+      </c>
+      <c r="AN7" s="13" t="n">
+        <v>766</v>
+      </c>
+      <c r="AO7" s="13" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="AP7" s="13" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="AQ7" s="13" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AR7" s="14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AS7" s="14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AT7" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU7" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV7" s="14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW7" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AX7" s="13" t="n">
+        <v>3260</v>
+      </c>
+      <c r="AY7" s="13" t="n">
+        <v>911</v>
+      </c>
+      <c r="AZ7" s="13" t="n">
+        <v>684</v>
+      </c>
+      <c r="BA7" s="13" t="n">
+        <v>93.54000000000001</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>▶  Sorted by EBITDA YoY Q%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Result Date</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Industry Group</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Subsector</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Indices</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Market Cap (Cr)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Screener Ticker</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Net Profit (Cr)</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>PAT Margin%</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Sales QoQ%</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA QoQ%</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>NP QoQ%</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>EPS QoQ%</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>PAT Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="X10" s="5" t="inlineStr">
+        <is>
+          <t>Sales YoY Q%</t>
+        </is>
+      </c>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA YoY Q%</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>NP YoY Q%</t>
+        </is>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>EPS YoY Q%</t>
+        </is>
+      </c>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AC10" s="5" t="inlineStr">
+        <is>
+          <t>PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
+          <t>Prev Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AE10" s="5" t="inlineStr">
+        <is>
+          <t>Prev Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AF10" s="5" t="inlineStr">
+        <is>
+          <t>Prev Qtr NP</t>
+        </is>
+      </c>
+      <c r="AG10" s="5" t="inlineStr">
+        <is>
+          <t>Prev Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AH10" s="5" t="inlineStr">
+        <is>
+          <t>LY Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AI10" s="5" t="inlineStr">
+        <is>
+          <t>LY Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AJ10" s="5" t="inlineStr">
+        <is>
+          <t>LY Qtr NP</t>
+        </is>
+      </c>
+      <c r="AK10" s="5" t="inlineStr">
+        <is>
+          <t>LY Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AL10" s="5" t="inlineStr">
+        <is>
+          <t>FY Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="AM10" s="5" t="inlineStr">
+        <is>
+          <t>FY EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="AN10" s="5" t="inlineStr">
+        <is>
+          <t>FY NP (Cr)</t>
+        </is>
+      </c>
+      <c r="AO10" s="5" t="inlineStr">
+        <is>
+          <t>FY EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="AP10" s="5" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="AQ10" s="5" t="inlineStr">
+        <is>
+          <t>FY PAT Margin%</t>
+        </is>
+      </c>
+      <c r="AR10" s="5" t="inlineStr">
+        <is>
+          <t>FY Sales YoY%</t>
+        </is>
+      </c>
+      <c r="AS10" s="5" t="inlineStr">
+        <is>
+          <t>FY EBITDA YoY%</t>
+        </is>
+      </c>
+      <c r="AT10" s="5" t="inlineStr">
+        <is>
+          <t>FY NP YoY%</t>
+        </is>
+      </c>
+      <c r="AU10" s="5" t="inlineStr">
+        <is>
+          <t>FY EPS YoY%</t>
+        </is>
+      </c>
+      <c r="AV10" s="5" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AW10" s="5" t="inlineStr">
+        <is>
+          <t>FY PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AX10" s="5" t="inlineStr">
+        <is>
+          <t>Prev FY Sales</t>
+        </is>
+      </c>
+      <c r="AY10" s="5" t="inlineStr">
+        <is>
+          <t>Prev FY EBITDA</t>
+        </is>
+      </c>
+      <c r="AZ10" s="5" t="inlineStr">
+        <is>
+          <t>Prev FY NP</t>
+        </is>
+      </c>
+      <c r="BA10" s="5" t="inlineStr">
+        <is>
+          <t>Prev FY EPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="10" t="n">
+        <v>6175</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>472</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>327</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T11" s="12" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U11" s="12" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W11" s="12" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="X11" s="12" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AA11" s="12" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AD11" s="10" t="n">
+        <v>306</v>
+      </c>
+      <c r="AE11" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="AF11" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG11" s="10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH11" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="AI11" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ11" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AK11" s="10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL11" s="10" t="n">
+        <v>1165</v>
+      </c>
+      <c r="AM11" s="10" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN11" s="10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO11" s="10" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AP11" s="10" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AQ11" s="10" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AR11" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AS11" s="12" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AT11" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU11" s="12" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AV11" s="12" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AW11" s="12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AX11" s="10" t="n">
+        <v>965</v>
+      </c>
+      <c r="AY11" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="AZ11" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="BA11" s="10" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Other Financial Services</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150, Nifty 500</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>31827</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>4340</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>1058</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>319</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>233</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="R12" s="15" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="S12" s="15" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="T12" s="15" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="U12" s="15" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="V12" s="15" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="W12" s="15" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X12" s="14" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Y12" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Z12" s="14" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AA12" s="14" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AB12" s="14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC12" s="14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD12" s="13" t="n">
+        <v>1082</v>
+      </c>
+      <c r="AE12" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF12" s="13" t="n">
+        <v>242</v>
+      </c>
+      <c r="AG12" s="13" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AH12" s="13" t="n">
+        <v>813</v>
+      </c>
+      <c r="AI12" s="13" t="n">
+        <v>232</v>
+      </c>
+      <c r="AJ12" s="13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK12" s="13" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AL12" s="13" t="n">
+        <v>3649</v>
+      </c>
+      <c r="AM12" s="13" t="n">
+        <v>1085</v>
+      </c>
+      <c r="AN12" s="13" t="n">
+        <v>766</v>
+      </c>
+      <c r="AO12" s="13" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="AP12" s="13" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="AQ12" s="13" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AR12" s="14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AS12" s="14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AT12" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU12" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV12" s="14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW12" s="14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AX12" s="13" t="n">
+        <v>3260</v>
+      </c>
+      <c r="AY12" s="13" t="n">
+        <v>911</v>
+      </c>
+      <c r="AZ12" s="13" t="n">
+        <v>684</v>
+      </c>
+      <c r="BA12" s="13" t="n">
+        <v>93.54000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>M B Agro Prod.</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="n">
+        <v>4430</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>506</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>395</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="R13" s="11" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="S13" s="11" t="n">
+        <v>-37.9</v>
+      </c>
+      <c r="T13" s="12" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U13" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="V13" s="11" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="W13" s="12" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="X13" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="Z13" s="12" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA13" s="12" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="AB13" s="11" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="AC13" s="12" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AD13" s="10" t="n">
+        <v>612</v>
+      </c>
+      <c r="AE13" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF13" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG13" s="10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH13" s="10" t="n">
+        <v>297</v>
+      </c>
+      <c r="AI13" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ13" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK13" s="10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL13" s="10" t="n">
+        <v>1867</v>
+      </c>
+      <c r="AM13" s="10" t="n">
+        <v>227</v>
+      </c>
+      <c r="AN13" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO13" s="10" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="AP13" s="10" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AQ13" s="10" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AR13" s="12" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AS13" s="12" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AT13" s="12" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="AU13" s="12" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="AV13" s="11" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AW13" s="12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AX13" s="10" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AY13" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="AZ13" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="BA13" s="10" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Lloyds Luxuries</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr"/>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr"/>
+      <c r="G14" s="13" t="n">
+        <v>197</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>LLOYDS</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P14" s="13" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="Q14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S14" s="13" t="inlineStr"/>
+      <c r="T14" s="13" t="inlineStr"/>
+      <c r="U14" s="13" t="inlineStr"/>
+      <c r="V14" s="14" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="W14" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="X14" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y14" s="13" t="inlineStr"/>
+      <c r="Z14" s="13" t="inlineStr"/>
+      <c r="AA14" s="13" t="inlineStr"/>
+      <c r="AB14" s="14" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="AC14" s="14" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AD14" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE14" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF14" s="13" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AG14" s="13" t="n">
+        <v>-14.55</v>
+      </c>
+      <c r="AH14" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" s="13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ14" s="13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AK14" s="13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL14" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AM14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="13" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AO14" s="13" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="AP14" s="13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ14" s="13" t="n">
+        <v>-55.74</v>
+      </c>
+      <c r="AR14" s="14" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AS14" s="13" t="inlineStr"/>
+      <c r="AT14" s="13" t="inlineStr"/>
+      <c r="AU14" s="13" t="inlineStr"/>
+      <c r="AV14" s="14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AW14" s="15" t="n">
+        <v>-40.52</v>
+      </c>
+      <c r="AX14" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AY14" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ14" s="13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BA14" s="13" t="n">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>▶  Sorted by NP YoY Q%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Result Date</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Industry Group</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Subsector</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Indices</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Market Cap (Cr)</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Screener Ticker</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Net Profit (Cr)</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>PAT Margin%</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>Sales QoQ%</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA QoQ%</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>NP QoQ%</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>EPS QoQ%</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>PAT Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>Sales YoY Q%</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA YoY Q%</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>NP YoY Q%</t>
+        </is>
+      </c>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>EPS YoY Q%</t>
+        </is>
+      </c>
+      <c r="AB17" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AC17" s="7" t="inlineStr">
+        <is>
+          <t>PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>Prev Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>Prev Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
+        <is>
+          <t>Prev Qtr NP</t>
+        </is>
+      </c>
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>Prev Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AH17" s="7" t="inlineStr">
+        <is>
+          <t>LY Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AI17" s="7" t="inlineStr">
+        <is>
+          <t>LY Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AJ17" s="7" t="inlineStr">
+        <is>
+          <t>LY Qtr NP</t>
+        </is>
+      </c>
+      <c r="AK17" s="7" t="inlineStr">
+        <is>
+          <t>LY Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AL17" s="7" t="inlineStr">
+        <is>
+          <t>FY Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="AM17" s="7" t="inlineStr">
+        <is>
+          <t>FY EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="AN17" s="7" t="inlineStr">
+        <is>
+          <t>FY NP (Cr)</t>
+        </is>
+      </c>
+      <c r="AO17" s="7" t="inlineStr">
+        <is>
+          <t>FY EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="AP17" s="7" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="AQ17" s="7" t="inlineStr">
+        <is>
+          <t>FY PAT Margin%</t>
+        </is>
+      </c>
+      <c r="AR17" s="7" t="inlineStr">
+        <is>
+          <t>FY Sales YoY%</t>
+        </is>
+      </c>
+      <c r="AS17" s="7" t="inlineStr">
+        <is>
+          <t>FY EBITDA YoY%</t>
+        </is>
+      </c>
+      <c r="AT17" s="7" t="inlineStr">
+        <is>
+          <t>FY NP YoY%</t>
+        </is>
+      </c>
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>FY EPS YoY%</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AW17" s="7" t="inlineStr">
+        <is>
+          <t>FY PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AX17" s="7" t="inlineStr">
+        <is>
+          <t>Prev FY Sales</t>
+        </is>
+      </c>
+      <c r="AY17" s="7" t="inlineStr">
+        <is>
+          <t>Prev FY EBITDA</t>
+        </is>
+      </c>
+      <c r="AZ17" s="7" t="inlineStr">
+        <is>
+          <t>Prev FY NP</t>
+        </is>
+      </c>
+      <c r="BA17" s="7" t="inlineStr">
+        <is>
+          <t>Prev FY EPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>M B Agro Prod.</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="10" t="n">
+        <v>4430</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>506</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>395</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q18" s="10" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="S18" s="11" t="n">
+        <v>-37.9</v>
+      </c>
+      <c r="T18" s="12" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U18" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="V18" s="11" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="W18" s="12" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="X18" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y18" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="Z18" s="12" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA18" s="12" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="AB18" s="11" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="AC18" s="12" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AD18" s="10" t="n">
+        <v>612</v>
+      </c>
+      <c r="AE18" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF18" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG18" s="10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH18" s="10" t="n">
+        <v>297</v>
+      </c>
+      <c r="AI18" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ18" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK18" s="10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL18" s="10" t="n">
+        <v>1867</v>
+      </c>
+      <c r="AM18" s="10" t="n">
+        <v>227</v>
+      </c>
+      <c r="AN18" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO18" s="10" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="AP18" s="10" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AQ18" s="10" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AR18" s="12" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AS18" s="12" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AT18" s="12" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="AU18" s="12" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="AV18" s="11" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AW18" s="12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AX18" s="10" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AY18" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="AZ18" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="BA18" s="10" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr"/>
+      <c r="G19" s="13" t="n">
+        <v>6175</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>472</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>327</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="Q19" s="13" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="R19" s="14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="S19" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T19" s="14" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V19" s="14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Y19" s="14" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="Z19" s="14" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AA19" s="14" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AB19" s="14" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AC19" s="14" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AD19" s="13" t="n">
+        <v>306</v>
+      </c>
+      <c r="AE19" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="AF19" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG19" s="13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH19" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="AI19" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ19" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AK19" s="13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL19" s="13" t="n">
+        <v>1165</v>
+      </c>
+      <c r="AM19" s="13" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN19" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO19" s="13" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AP19" s="13" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AQ19" s="13" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AR19" s="14" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AS19" s="14" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AT19" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU19" s="14" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AV19" s="14" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AW19" s="14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AX19" s="13" t="n">
+        <v>965</v>
+      </c>
+      <c r="AY19" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AZ19" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="BA19" s="13" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Other Financial Services</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150, Nifty 500</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>31827</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>4340</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>1058</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>319</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>233</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="Q20" s="10" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="U20" s="11" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="V20" s="11" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="W20" s="11" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X20" s="12" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Y20" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Z20" s="12" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AA20" s="12" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AB20" s="12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC20" s="12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD20" s="10" t="n">
+        <v>1082</v>
+      </c>
+      <c r="AE20" s="10" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF20" s="10" t="n">
+        <v>242</v>
+      </c>
+      <c r="AG20" s="10" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AH20" s="10" t="n">
+        <v>813</v>
+      </c>
+      <c r="AI20" s="10" t="n">
+        <v>232</v>
+      </c>
+      <c r="AJ20" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK20" s="10" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AL20" s="10" t="n">
+        <v>3649</v>
+      </c>
+      <c r="AM20" s="10" t="n">
+        <v>1085</v>
+      </c>
+      <c r="AN20" s="10" t="n">
+        <v>766</v>
+      </c>
+      <c r="AO20" s="10" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="AP20" s="10" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="AQ20" s="10" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AR20" s="12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AS20" s="12" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AT20" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU20" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV20" s="12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW20" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AX20" s="10" t="n">
+        <v>3260</v>
+      </c>
+      <c r="AY20" s="10" t="n">
+        <v>911</v>
+      </c>
+      <c r="AZ20" s="10" t="n">
+        <v>684</v>
+      </c>
+      <c r="BA20" s="10" t="n">
+        <v>93.54000000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Lloyds Luxuries</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="13" t="n">
+        <v>197</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>LLOYDS</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P21" s="13" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="Q21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S21" s="13" t="inlineStr"/>
+      <c r="T21" s="13" t="inlineStr"/>
+      <c r="U21" s="13" t="inlineStr"/>
+      <c r="V21" s="14" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="W21" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="X21" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y21" s="13" t="inlineStr"/>
+      <c r="Z21" s="13" t="inlineStr"/>
+      <c r="AA21" s="13" t="inlineStr"/>
+      <c r="AB21" s="14" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="AC21" s="14" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AD21" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE21" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF21" s="13" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AG21" s="13" t="n">
+        <v>-14.55</v>
+      </c>
+      <c r="AH21" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI21" s="13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ21" s="13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AK21" s="13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL21" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AM21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" s="13" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AO21" s="13" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="AP21" s="13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ21" s="13" t="n">
+        <v>-55.74</v>
+      </c>
+      <c r="AR21" s="14" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AS21" s="13" t="inlineStr"/>
+      <c r="AT21" s="13" t="inlineStr"/>
+      <c r="AU21" s="13" t="inlineStr"/>
+      <c r="AV21" s="14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AW21" s="15" t="n">
+        <v>-40.52</v>
+      </c>
+      <c r="AX21" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AY21" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ21" s="13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BA21" s="13" t="n">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>▶  Sorted by EPS YoY Q%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Result Date</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Industry Group</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Subsector</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Indices</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Market Cap (Cr)</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Screener Ticker</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>Net Profit (Cr)</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>PAT Margin%</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>Sales QoQ%</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA QoQ%</t>
+        </is>
+      </c>
+      <c r="T24" s="9" t="inlineStr">
+        <is>
+          <t>NP QoQ%</t>
+        </is>
+      </c>
+      <c r="U24" s="9" t="inlineStr">
+        <is>
+          <t>EPS QoQ%</t>
+        </is>
+      </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>PAT Margin QoQ pp</t>
+        </is>
+      </c>
+      <c r="X24" s="9" t="inlineStr">
+        <is>
+          <t>Sales YoY Q%</t>
+        </is>
+      </c>
+      <c r="Y24" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA YoY Q%</t>
+        </is>
+      </c>
+      <c r="Z24" s="9" t="inlineStr">
+        <is>
+          <t>NP YoY Q%</t>
+        </is>
+      </c>
+      <c r="AA24" s="9" t="inlineStr">
+        <is>
+          <t>EPS YoY Q%</t>
+        </is>
+      </c>
+      <c r="AB24" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AC24" s="9" t="inlineStr">
+        <is>
+          <t>PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AD24" s="9" t="inlineStr">
+        <is>
+          <t>Prev Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AE24" s="9" t="inlineStr">
+        <is>
+          <t>Prev Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AF24" s="9" t="inlineStr">
+        <is>
+          <t>Prev Qtr NP</t>
+        </is>
+      </c>
+      <c r="AG24" s="9" t="inlineStr">
+        <is>
+          <t>Prev Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AH24" s="9" t="inlineStr">
+        <is>
+          <t>LY Qtr Sales</t>
+        </is>
+      </c>
+      <c r="AI24" s="9" t="inlineStr">
+        <is>
+          <t>LY Qtr EBITDA</t>
+        </is>
+      </c>
+      <c r="AJ24" s="9" t="inlineStr">
+        <is>
+          <t>LY Qtr NP</t>
+        </is>
+      </c>
+      <c r="AK24" s="9" t="inlineStr">
+        <is>
+          <t>LY Qtr EPS</t>
+        </is>
+      </c>
+      <c r="AL24" s="9" t="inlineStr">
+        <is>
+          <t>FY Sales (Cr)</t>
+        </is>
+      </c>
+      <c r="AM24" s="9" t="inlineStr">
+        <is>
+          <t>FY EBITDA (Cr)</t>
+        </is>
+      </c>
+      <c r="AN24" s="9" t="inlineStr">
+        <is>
+          <t>FY NP (Cr)</t>
+        </is>
+      </c>
+      <c r="AO24" s="9" t="inlineStr">
+        <is>
+          <t>FY EPS (Rs)</t>
+        </is>
+      </c>
+      <c r="AP24" s="9" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin%</t>
+        </is>
+      </c>
+      <c r="AQ24" s="9" t="inlineStr">
+        <is>
+          <t>FY PAT Margin%</t>
+        </is>
+      </c>
+      <c r="AR24" s="9" t="inlineStr">
+        <is>
+          <t>FY Sales YoY%</t>
+        </is>
+      </c>
+      <c r="AS24" s="9" t="inlineStr">
+        <is>
+          <t>FY EBITDA YoY%</t>
+        </is>
+      </c>
+      <c r="AT24" s="9" t="inlineStr">
+        <is>
+          <t>FY NP YoY%</t>
+        </is>
+      </c>
+      <c r="AU24" s="9" t="inlineStr">
+        <is>
+          <t>FY EPS YoY%</t>
+        </is>
+      </c>
+      <c r="AV24" s="9" t="inlineStr">
+        <is>
+          <t>FY EBITDA Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>FY PAT Margin YoY pp</t>
+        </is>
+      </c>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>Prev FY Sales</t>
+        </is>
+      </c>
+      <c r="AY24" s="9" t="inlineStr">
+        <is>
+          <t>Prev FY EBITDA</t>
+        </is>
+      </c>
+      <c r="AZ24" s="9" t="inlineStr">
+        <is>
+          <t>Prev FY NP</t>
+        </is>
+      </c>
+      <c r="BA24" s="9" t="inlineStr">
+        <is>
+          <t>Prev FY EPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>M B Agro Prod.</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Fertilizers</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="n">
+        <v>4430</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>506</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>395</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>-35.5</v>
+      </c>
+      <c r="S25" s="11" t="n">
+        <v>-37.9</v>
+      </c>
+      <c r="T25" s="12" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="U25" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="V25" s="11" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="W25" s="12" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="X25" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y25" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="Z25" s="12" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="AA25" s="12" t="n">
+        <v>318.4</v>
+      </c>
+      <c r="AB25" s="11" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="AC25" s="12" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="AD25" s="10" t="n">
+        <v>612</v>
+      </c>
+      <c r="AE25" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF25" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG25" s="10" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH25" s="10" t="n">
+        <v>297</v>
+      </c>
+      <c r="AI25" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ25" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK25" s="10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL25" s="10" t="n">
+        <v>1867</v>
+      </c>
+      <c r="AM25" s="10" t="n">
+        <v>227</v>
+      </c>
+      <c r="AN25" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO25" s="10" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="AP25" s="10" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AQ25" s="10" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="AR25" s="12" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AS25" s="12" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AT25" s="12" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="AU25" s="12" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="AV25" s="11" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AW25" s="12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AX25" s="10" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AY25" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="AZ25" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="BA25" s="10" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Bajaj Consumer</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr"/>
+      <c r="G26" s="13" t="n">
+        <v>6175</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>472</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>327</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P26" s="13" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="Q26" s="13" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="R26" s="14" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="S26" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="T26" s="14" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="U26" s="14" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="V26" s="14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W26" s="14" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="X26" s="14" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="Y26" s="14" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="Z26" s="14" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AA26" s="14" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AB26" s="14" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AC26" s="14" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="AD26" s="13" t="n">
+        <v>306</v>
+      </c>
+      <c r="AE26" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="AF26" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG26" s="13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH26" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="AI26" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ26" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="AK26" s="13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AL26" s="13" t="n">
+        <v>1165</v>
+      </c>
+      <c r="AM26" s="13" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN26" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO26" s="13" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AP26" s="13" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AQ26" s="13" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="AR26" s="14" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AS26" s="14" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="AT26" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="AU26" s="14" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AV26" s="14" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AW26" s="14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AX26" s="13" t="n">
+        <v>965</v>
+      </c>
+      <c r="AY26" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AZ26" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="BA26" s="13" t="n">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Other Financial Services</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Nifty Midcap 150, Nifty 500</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>31827</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>4340</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>1058</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>319</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>233</v>
+      </c>
+      <c r="O27" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="P27" s="10" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="R27" s="11" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="S27" s="11" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="T27" s="11" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="U27" s="11" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="V27" s="11" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="W27" s="11" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="X27" s="12" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Y27" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Z27" s="12" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AA27" s="12" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="AB27" s="12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC27" s="12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD27" s="10" t="n">
+        <v>1082</v>
+      </c>
+      <c r="AE27" s="10" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF27" s="10" t="n">
+        <v>242</v>
+      </c>
+      <c r="AG27" s="10" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AH27" s="10" t="n">
+        <v>813</v>
+      </c>
+      <c r="AI27" s="10" t="n">
+        <v>232</v>
+      </c>
+      <c r="AJ27" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK27" s="10" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AL27" s="10" t="n">
+        <v>3649</v>
+      </c>
+      <c r="AM27" s="10" t="n">
+        <v>1085</v>
+      </c>
+      <c r="AN27" s="10" t="n">
+        <v>766</v>
+      </c>
+      <c r="AO27" s="10" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="AP27" s="10" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="AQ27" s="10" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AR27" s="12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AS27" s="12" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AT27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV27" s="12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW27" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AX27" s="10" t="n">
+        <v>3260</v>
+      </c>
+      <c r="AY27" s="10" t="n">
+        <v>911</v>
+      </c>
+      <c r="AZ27" s="10" t="n">
+        <v>684</v>
+      </c>
+      <c r="BA27" s="10" t="n">
+        <v>93.54000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>17 Apr 2026</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Lloyds Luxuries</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr"/>
+      <c r="E28" s="13" t="inlineStr"/>
+      <c r="F28" s="13" t="inlineStr"/>
+      <c r="G28" s="13" t="n">
+        <v>197</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>LLOYDS</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P28" s="13" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="Q28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="14" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S28" s="13" t="inlineStr"/>
+      <c r="T28" s="13" t="inlineStr"/>
+      <c r="U28" s="13" t="inlineStr"/>
+      <c r="V28" s="14" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="W28" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="X28" s="14" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Y28" s="13" t="inlineStr"/>
+      <c r="Z28" s="13" t="inlineStr"/>
+      <c r="AA28" s="13" t="inlineStr"/>
+      <c r="AB28" s="14" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="AC28" s="14" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="AD28" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE28" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF28" s="13" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AG28" s="13" t="n">
+        <v>-14.55</v>
+      </c>
+      <c r="AH28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI28" s="13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ28" s="13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AK28" s="13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL28" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="AM28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="13" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AO28" s="13" t="n">
+        <v>-14.24</v>
+      </c>
+      <c r="AP28" s="13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AQ28" s="13" t="n">
+        <v>-55.74</v>
+      </c>
+      <c r="AR28" s="14" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AS28" s="13" t="inlineStr"/>
+      <c r="AT28" s="13" t="inlineStr"/>
+      <c r="AU28" s="13" t="inlineStr"/>
+      <c r="AV28" s="14" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AW28" s="15" t="n">
+        <v>-40.52</v>
+      </c>
+      <c r="AX28" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AY28" s="13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AZ28" s="13" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BA28" s="13" t="n">
+        <v>-2.79</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A9:BA9"/>
+    <mergeCell ref="A16:BA16"/>
+    <mergeCell ref="A2:BA2"/>
+    <mergeCell ref="A1:BA1"/>
+    <mergeCell ref="A23:BA23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>